--- a/data/trans_orig/IP13_R2_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP13_R2_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si limitaron su actividad por síntomas en 2023 (tasa de respuesta: 99,95%)</t>
+          <t>Menores según si en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por síntomas en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7253</t>
+          <t>7767</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2141</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10075</t>
+          <t>10462</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66029</t>
+          <t>65515</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72490</t>
+          <t>72019</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73354</t>
+          <t>73488</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>142573</t>
+          <t>142186</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>150507</t>
+          <t>150724</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1583</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9744</t>
+          <t>10259</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7626</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14040</t>
+          <t>13483</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>117095</t>
+          <t>116580</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>125295</t>
+          <t>125256</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>120092</t>
+          <t>119970</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>126316</t>
+          <t>126308</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>240395</t>
+          <t>240952</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>250543</t>
+          <t>250630</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>926</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6843</t>
+          <t>7141</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>712</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>7675</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2315</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10452</t>
+          <t>11834</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51425</t>
+          <t>51127</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57620</t>
+          <t>57342</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60008</t>
+          <t>59488</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66479</t>
+          <t>66451</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>114979</t>
+          <t>113597</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>123116</t>
+          <t>123118</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5226</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7366</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>629</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8805</t>
+          <t>8453</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64917</t>
+          <t>65116</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>70768</t>
+          <t>72231</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>139473</t>
+          <t>139825</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>147672</t>
+          <t>147649</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>994</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5817</t>
+          <t>5565</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>581</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>5846</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>2246</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9099</t>
+          <t>9684</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,87%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28696</t>
+          <t>28948</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33598</t>
+          <t>33519</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34418</t>
+          <t>34873</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40087</t>
+          <t>40138</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>66133</t>
+          <t>65548</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>72880</t>
+          <t>72986</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>536</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5040</t>
+          <t>4887</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>7100</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2414</t>
+          <t>2246</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9775</t>
+          <t>9860</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41127</t>
+          <t>41280</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45644</t>
+          <t>45631</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>49259</t>
+          <t>49086</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>55055</t>
+          <t>55086</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>92578</t>
+          <t>92493</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>99939</t>
+          <t>100107</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3140</t>
+          <t>2939</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11606</t>
+          <t>11771</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7938</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20529</t>
+          <t>21319</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12935</t>
+          <t>13374</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28869</t>
+          <t>27822</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>112902</t>
+          <t>112737</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>121368</t>
+          <t>121569</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>134759</t>
+          <t>133969</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>147350</t>
+          <t>147288</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>250928</t>
+          <t>251975</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>266862</t>
+          <t>266423</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,22%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8295</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4181</t>
+          <t>4187</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14363</t>
+          <t>14162</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7614</t>
+          <t>7617</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19216</t>
+          <t>19149</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>123487</t>
+          <t>123324</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>129753</t>
+          <t>129708</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>142432</t>
+          <t>142633</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>152614</t>
+          <t>152608</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>269198</t>
+          <t>269265</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>280800</t>
+          <t>280797</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>19011</t>
+          <t>18874</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>36467</t>
+          <t>35042</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>26271</t>
+          <t>27485</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>47471</t>
+          <t>48516</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>51509</t>
+          <t>51166</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>77482</t>
+          <t>77859</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>628873</t>
+          <t>630298</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>646329</t>
+          <t>646466</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>713777</t>
+          <t>712732</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>734977</t>
+          <t>733763</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1349106</t>
+          <t>1348729</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1375079</t>
+          <t>1375422</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,41%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP13_R2_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP13_R2_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1529</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5679</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,85%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3420</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1263</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7767</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,6%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>3068</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>6591</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5251</t>
+          <t>4597</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1871</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10462</t>
+          <t>9230</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>62616</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>58466</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,62%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>91,15%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>69862</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>65515</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>72019</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>95,33%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>89,4%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,28%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>77535</t>
+          <t>53413</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73488</t>
+          <t>49890</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>55354</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>147397</t>
+          <t>116029</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>142186</t>
+          <t>111396</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>150724</t>
+          <t>118755</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>2904</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1583</t>
+          <t>986</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10259</t>
+          <t>6462</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>4454</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7626</t>
+          <t>8984</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>7729</t>
+          <t>7358</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>3918</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13483</t>
+          <t>13125</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>112931</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>109373</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>114849</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,49%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>94,42%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,15%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>122515</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>116580</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>125256</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>96,59%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,91%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,75%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>124191</t>
+          <t>96096</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>119970</t>
+          <t>91566</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>126308</t>
+          <t>98971</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>246706</t>
+          <t>209027</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>240952</t>
+          <t>203260</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>250630</t>
+          <t>212467</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>126839</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>126839</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>126839</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>100550</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>100550</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>100550</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>254435</t>
+          <t>216385</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>254435</t>
+          <t>216385</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>254435</t>
+          <t>216385</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2240</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>557</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5802</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,77%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2738</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>926</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7141</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,7%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,26%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2703</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>644</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7675</t>
+          <t>5851</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>5441</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2191</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11834</t>
+          <t>8965</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>57137</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>53575</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>58820</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,23%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>90,23%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,06%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>55530</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>51127</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>57342</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>95,3%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>87,74%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,41%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>64460</t>
+          <t>53987</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59488</t>
+          <t>50707</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66451</t>
+          <t>55914</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>119990</t>
+          <t>111125</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>113597</t>
+          <t>106971</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>123118</t>
+          <t>113745</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1186</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5796</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,03%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1496</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1639</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5027</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7207</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,17%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1244</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5903</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>2825</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>542</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8453</t>
+          <t>9098</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -1862,74 +1862,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>70976</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>66366</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,36%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,97%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>68647</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>65116</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>97,87%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,83%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>69205</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>63637</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>70844</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>97,69%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>89,83%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>76890</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>72231</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>78134</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,41%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>92,45%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>159</t>
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>145538</t>
+          <t>140180</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>139825</t>
+          <t>133907</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>147649</t>
+          <t>142463</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2610</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6259</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,6%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>15,81%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2530</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>994</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5565</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7,33%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>16,12%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2526</t>
+          <t>2595</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>808</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5057</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2246</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9684</t>
+          <t>9772</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,0%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>36969</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>33320</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>38939</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,4%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>84,19%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,38%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>31983</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>28948</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>33519</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>92,67%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>83,88%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,12%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>38193</t>
+          <t>33013</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34873</t>
+          <t>29893</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40138</t>
+          <t>34800</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>70175</t>
+          <t>69982</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>65548</t>
+          <t>65415</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>72986</t>
+          <t>72645</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,62%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2798</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1108</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>6684</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>5,72%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>13,66%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>1761</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>536</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4887</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>3,81%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>10,59%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>558</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7100</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2246</t>
+          <t>2081</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9860</t>
+          <t>8281</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>46144</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>42258</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>47834</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>94,28%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>86,34%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>97,74%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>44406</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>41280</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>45631</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>96,19%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>89,41%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>98,84%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>52917</t>
+          <t>44029</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>49086</t>
+          <t>41151</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>55086</t>
+          <t>45208</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>97324</t>
+          <t>90173</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>92493</t>
+          <t>86427</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>100107</t>
+          <t>92627</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>12882</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>7746</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>19739</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>9,15%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>14,02%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>6331</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>2939</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>11771</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>5,08%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>9,45%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>13536</t>
+          <t>6471</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>3216</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21319</t>
+          <t>11935</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>19867</t>
+          <t>19352</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13374</t>
+          <t>12715</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>27822</t>
+          <t>27323</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>127949</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>121092</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>133085</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>90,85%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>85,98%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>94,5%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>118177</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>112737</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>121569</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>94,92%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>90,55%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>97,64%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>141752</t>
+          <t>116058</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>133969</t>
+          <t>110594</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>147288</t>
+          <t>119313</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>259930</t>
+          <t>244009</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>251975</t>
+          <t>236038</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>266423</t>
+          <t>250646</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>140831</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>140831</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>140831</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>124508</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>124508</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>124508</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>155288</t>
+          <t>122529</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>155288</t>
+          <t>122529</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>155288</t>
+          <t>122529</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>279797</t>
+          <t>263361</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>279797</t>
+          <t>263361</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>279797</t>
+          <t>263361</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,74 +3121,74 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>8085</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>3992</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>13937</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>5,07%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>8,74%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>4258</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>1911</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>8295</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>6,3%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>8039</t>
+          <t>3705</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4187</t>
+          <t>1581</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14162</t>
+          <t>7208</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
           <t>5,13%</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>9,03%</t>
-        </is>
-      </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>20</t>
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>12297</t>
+          <t>11791</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7617</t>
+          <t>6772</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19149</t>
+          <t>18403</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>151336</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>145484</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>155429</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>94,93%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>91,26%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>97,5%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>127361</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>123324</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>129708</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>96,77%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>93,7%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>98,55%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>148756</t>
+          <t>136792</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>142633</t>
+          <t>133289</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>152608</t>
+          <t>138916</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
+          <t>97,36%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
           <t>94,87%</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>90,97%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>276117</t>
+          <t>288127</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>269265</t>
+          <t>281515</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>280797</t>
+          <t>293146</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,74%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>34234</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>26014</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>44933</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>3,71%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>6,42%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>26858</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>18874</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>35042</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>36553</t>
+          <t>26239</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>27485</t>
+          <t>18945</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>48516</t>
+          <t>35016</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>63411</t>
+          <t>60473</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>51166</t>
+          <t>49431</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>77859</t>
+          <t>74402</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>926</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>666059</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>655360</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>674279</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>95,11%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>93,58%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>96,29%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>900</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>638482</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>630298</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>646466</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>95,96%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>94,73%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>97,16%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>926</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>724695</t>
+          <t>602594</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>712732</t>
+          <t>593817</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>733763</t>
+          <t>609888</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1363177</t>
+          <t>1268652</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1348729</t>
+          <t>1254723</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1375422</t>
+          <t>1279694</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,28%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1426588</t>
+          <t>1329125</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1426588</t>
+          <t>1329125</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1426588</t>
+          <t>1329125</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
